--- a/app/reports/COE_research.xlsx
+++ b/app/reports/COE_research.xlsx
@@ -620,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-07-20 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-07-21 17:37 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>16.795</v>
+        <v>16.615</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.04604000091552735</v>
+        <v>0.04625999927520752</v>
       </c>
     </row>
     <row r="6">
@@ -1197,7 +1197,7 @@
         </is>
       </c>
       <c r="B35" s="20" t="n">
-        <v>6007315.034236379</v>
+        <v>6007314.835991574</v>
       </c>
     </row>
     <row r="36">
@@ -1218,7 +1218,7 @@
         </is>
       </c>
       <c r="B37" s="22" t="n">
-        <v>16.795</v>
+        <v>16.615</v>
       </c>
     </row>
     <row r="38">
@@ -1497,14 +1497,14 @@
         </is>
       </c>
       <c r="C5" s="30" t="n">
-        <v>100892856</v>
+        <v>99811536</v>
       </c>
       <c r="D5" s="31" t="n"/>
       <c r="E5" s="31" t="n">
-        <v>-4.58</v>
+        <v>-4.8</v>
       </c>
       <c r="F5" s="31" t="n">
-        <v>0.58</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="6">
@@ -1519,16 +1519,16 @@
         </is>
       </c>
       <c r="C6" s="32" t="n">
-        <v>4528441</v>
+        <v>6860822</v>
       </c>
       <c r="D6" s="33" t="n">
-        <v>0.008287509</v>
+        <v>0.008130399999999999</v>
       </c>
       <c r="E6" s="33" t="n">
-        <v>-0.732</v>
+        <v>-0.712</v>
       </c>
       <c r="F6" s="33" t="n">
-        <v>1.156</v>
+        <v>1.125</v>
       </c>
     </row>
     <row r="7">
@@ -1543,16 +1543,16 @@
         </is>
       </c>
       <c r="C7" s="32" t="n">
-        <v>2559402</v>
+        <v>2652998</v>
       </c>
       <c r="D7" s="33" t="n">
-        <v>0.010029282</v>
+        <v>0.010396047</v>
       </c>
       <c r="E7" s="33" t="n">
-        <v>6.173</v>
+        <v>6.177</v>
       </c>
       <c r="F7" s="33" t="n">
-        <v>-7.969</v>
+        <v>-7.973</v>
       </c>
     </row>
     <row r="8">
@@ -1567,14 +1567,14 @@
         </is>
       </c>
       <c r="C8" s="32" t="n">
-        <v>7881176</v>
+        <v>8230226</v>
       </c>
       <c r="D8" s="33" t="n"/>
       <c r="E8" s="33" t="n">
-        <v>-3.022</v>
+        <v>-3.008</v>
       </c>
       <c r="F8" s="33" t="n">
-        <v>3905.878</v>
+        <v>3887.76</v>
       </c>
     </row>
     <row r="9">
@@ -1589,16 +1589,16 @@
         </is>
       </c>
       <c r="C9" s="32" t="n">
-        <v>3355261</v>
+        <v>3426347</v>
       </c>
       <c r="D9" s="33" t="n">
-        <v>0.0054915645</v>
+        <v>0.005607912</v>
       </c>
       <c r="E9" s="33" t="n">
-        <v>1.031</v>
+        <v>1.012</v>
       </c>
       <c r="F9" s="33" t="n">
-        <v>-1.363</v>
+        <v>-1.338</v>
       </c>
     </row>
     <row r="10">
@@ -1613,14 +1613,14 @@
         </is>
       </c>
       <c r="C10" s="32" t="n">
-        <v>1765857</v>
+        <v>1830902</v>
       </c>
       <c r="D10" s="33" t="n"/>
       <c r="E10" s="33" t="n">
-        <v>-0.445</v>
+        <v>-0.437</v>
       </c>
       <c r="F10" s="33" t="n">
-        <v>0.237</v>
+        <v>0.233</v>
       </c>
     </row>
     <row r="11">
@@ -1667,14 +1667,14 @@
         </is>
       </c>
       <c r="C13" s="32" t="n">
-        <v>1873504</v>
+        <v>1840999</v>
       </c>
       <c r="D13" s="33" t="n"/>
       <c r="E13" s="33" t="n">
-        <v>-0.01</v>
+        <v>0.041</v>
       </c>
       <c r="F13" s="33" t="n">
-        <v>0.194</v>
+        <v>-0.832</v>
       </c>
     </row>
     <row r="15">

--- a/app/reports/COE_research.xlsx
+++ b/app/reports/COE_research.xlsx
@@ -620,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-07-21 17:37 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-07-22 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>16.615</v>
+        <v>15.75</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.04625999927520752</v>
+        <v>0.04654000282287598</v>
       </c>
     </row>
     <row r="6">
@@ -1197,7 +1197,7 @@
         </is>
       </c>
       <c r="B35" s="20" t="n">
-        <v>6007314.835991574</v>
+        <v>6007314.793650794</v>
       </c>
     </row>
     <row r="36">
@@ -1218,7 +1218,7 @@
         </is>
       </c>
       <c r="B37" s="22" t="n">
-        <v>16.615</v>
+        <v>15.75</v>
       </c>
     </row>
     <row r="38">
@@ -1497,14 +1497,14 @@
         </is>
       </c>
       <c r="C5" s="30" t="n">
-        <v>99811536</v>
+        <v>94615208</v>
       </c>
       <c r="D5" s="31" t="n"/>
       <c r="E5" s="31" t="n">
-        <v>-4.8</v>
+        <v>-4.5</v>
       </c>
       <c r="F5" s="31" t="n">
-        <v>0.61</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="6">
@@ -1519,16 +1519,16 @@
         </is>
       </c>
       <c r="C6" s="32" t="n">
-        <v>6860822</v>
+        <v>6976827</v>
       </c>
       <c r="D6" s="33" t="n">
-        <v>0.008130399999999999</v>
+        <v>0.008267871</v>
       </c>
       <c r="E6" s="33" t="n">
-        <v>-0.712</v>
+        <v>-0.7</v>
       </c>
       <c r="F6" s="33" t="n">
-        <v>1.125</v>
+        <v>1.106</v>
       </c>
     </row>
     <row r="7">
@@ -1543,16 +1543,16 @@
         </is>
       </c>
       <c r="C7" s="32" t="n">
-        <v>2652998</v>
+        <v>2802265</v>
       </c>
       <c r="D7" s="33" t="n">
-        <v>0.010396047</v>
+        <v>0.010980966</v>
       </c>
       <c r="E7" s="33" t="n">
-        <v>6.177</v>
+        <v>6.154</v>
       </c>
       <c r="F7" s="33" t="n">
-        <v>-7.973</v>
+        <v>-7.944</v>
       </c>
     </row>
     <row r="8">
@@ -1567,14 +1567,14 @@
         </is>
       </c>
       <c r="C8" s="32" t="n">
-        <v>8230226</v>
+        <v>7752578</v>
       </c>
       <c r="D8" s="33" t="n"/>
       <c r="E8" s="33" t="n">
-        <v>-3.008</v>
+        <v>-3.232</v>
       </c>
       <c r="F8" s="33" t="n">
-        <v>3887.76</v>
+        <v>4177.639</v>
       </c>
     </row>
     <row r="9">
@@ -1589,16 +1589,16 @@
         </is>
       </c>
       <c r="C9" s="32" t="n">
-        <v>3426347</v>
+        <v>3646714</v>
       </c>
       <c r="D9" s="33" t="n">
-        <v>0.005607912</v>
+        <v>0.0059685865</v>
       </c>
       <c r="E9" s="33" t="n">
-        <v>1.012</v>
+        <v>1.009</v>
       </c>
       <c r="F9" s="33" t="n">
-        <v>-1.338</v>
+        <v>-1.334</v>
       </c>
     </row>
     <row r="10">
@@ -1613,14 +1613,14 @@
         </is>
       </c>
       <c r="C10" s="32" t="n">
-        <v>1830902</v>
+        <v>1837166</v>
       </c>
       <c r="D10" s="33" t="n"/>
       <c r="E10" s="33" t="n">
-        <v>-0.437</v>
+        <v>-0.479</v>
       </c>
       <c r="F10" s="33" t="n">
-        <v>0.233</v>
+        <v>0.255</v>
       </c>
     </row>
     <row r="11">
@@ -1667,14 +1667,14 @@
         </is>
       </c>
       <c r="C13" s="32" t="n">
-        <v>1840999</v>
+        <v>1665817</v>
       </c>
       <c r="D13" s="33" t="n"/>
       <c r="E13" s="33" t="n">
-        <v>0.041</v>
+        <v>0.02</v>
       </c>
       <c r="F13" s="33" t="n">
-        <v>-0.832</v>
+        <v>-0.396</v>
       </c>
     </row>
     <row r="15">

--- a/app/reports/COE_research.xlsx
+++ b/app/reports/COE_research.xlsx
@@ -620,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-07-22 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-07-23 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>15.75</v>
+        <v>15.55</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.04654000282287598</v>
+        <v>0.04699000358581543</v>
       </c>
     </row>
     <row r="6">
@@ -1197,7 +1197,7 @@
         </is>
       </c>
       <c r="B35" s="20" t="n">
-        <v>6007314.793650794</v>
+        <v>6007315.241157556</v>
       </c>
     </row>
     <row r="36">
@@ -1218,7 +1218,7 @@
         </is>
       </c>
       <c r="B37" s="22" t="n">
-        <v>15.75</v>
+        <v>15.55</v>
       </c>
     </row>
     <row r="38">
@@ -1497,14 +1497,14 @@
         </is>
       </c>
       <c r="C5" s="30" t="n">
-        <v>94615208</v>
+        <v>93413752</v>
       </c>
       <c r="D5" s="31" t="n"/>
       <c r="E5" s="31" t="n">
-        <v>-4.5</v>
+        <v>-4.41</v>
       </c>
       <c r="F5" s="31" t="n">
-        <v>0.57</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -1519,16 +1519,16 @@
         </is>
       </c>
       <c r="C6" s="32" t="n">
-        <v>6976827</v>
+        <v>7490560</v>
       </c>
       <c r="D6" s="33" t="n">
-        <v>0.008267871</v>
+        <v>0.008876669</v>
       </c>
       <c r="E6" s="33" t="n">
-        <v>-0.7</v>
+        <v>-0.71</v>
       </c>
       <c r="F6" s="33" t="n">
-        <v>1.106</v>
+        <v>1.121</v>
       </c>
     </row>
     <row r="7">
@@ -1543,16 +1543,16 @@
         </is>
       </c>
       <c r="C7" s="32" t="n">
-        <v>2802265</v>
+        <v>2241812</v>
       </c>
       <c r="D7" s="33" t="n">
-        <v>0.010980966</v>
+        <v>0.008784772999999999</v>
       </c>
       <c r="E7" s="33" t="n">
-        <v>6.154</v>
+        <v>6.134</v>
       </c>
       <c r="F7" s="33" t="n">
-        <v>-7.944</v>
+        <v>-7.919</v>
       </c>
     </row>
     <row r="8">
@@ -1567,14 +1567,14 @@
         </is>
       </c>
       <c r="C8" s="32" t="n">
-        <v>7752578</v>
+        <v>7862805</v>
       </c>
       <c r="D8" s="33" t="n"/>
       <c r="E8" s="33" t="n">
-        <v>-3.232</v>
+        <v>-2.938</v>
       </c>
       <c r="F8" s="33" t="n">
-        <v>4177.639</v>
+        <v>3797.173</v>
       </c>
     </row>
     <row r="9">
@@ -1589,16 +1589,16 @@
         </is>
       </c>
       <c r="C9" s="32" t="n">
-        <v>3646714</v>
+        <v>3113569</v>
       </c>
       <c r="D9" s="33" t="n">
-        <v>0.0059685865</v>
+        <v>0.005095986</v>
       </c>
       <c r="E9" s="33" t="n">
-        <v>1.009</v>
+        <v>0.993</v>
       </c>
       <c r="F9" s="33" t="n">
-        <v>-1.334</v>
+        <v>-1.313</v>
       </c>
     </row>
     <row r="10">
@@ -1613,14 +1613,14 @@
         </is>
       </c>
       <c r="C10" s="32" t="n">
-        <v>1837166</v>
+        <v>1949429</v>
       </c>
       <c r="D10" s="33" t="n"/>
       <c r="E10" s="33" t="n">
-        <v>-0.479</v>
+        <v>-0.484</v>
       </c>
       <c r="F10" s="33" t="n">
-        <v>0.255</v>
+        <v>0.258</v>
       </c>
     </row>
     <row r="11">
@@ -1667,14 +1667,14 @@
         </is>
       </c>
       <c r="C13" s="32" t="n">
-        <v>1665817</v>
+        <v>1597930</v>
       </c>
       <c r="D13" s="33" t="n"/>
       <c r="E13" s="33" t="n">
-        <v>0.02</v>
+        <v>0.052</v>
       </c>
       <c r="F13" s="33" t="n">
-        <v>-0.396</v>
+        <v>-1.059</v>
       </c>
     </row>
     <row r="15">

--- a/app/reports/COE_research.xlsx
+++ b/app/reports/COE_research.xlsx
@@ -620,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-07-23 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-07-24 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>15.55</v>
+        <v>16.39</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.04699000358581543</v>
+        <v>0.04672999858856201</v>
       </c>
     </row>
     <row r="6">
@@ -1197,7 +1197,7 @@
         </is>
       </c>
       <c r="B35" s="20" t="n">
-        <v>6007315.241157556</v>
+        <v>6007314.704087858</v>
       </c>
     </row>
     <row r="36">
@@ -1218,7 +1218,7 @@
         </is>
       </c>
       <c r="B37" s="22" t="n">
-        <v>15.55</v>
+        <v>16.39</v>
       </c>
     </row>
     <row r="38">
@@ -1497,7 +1497,7 @@
         </is>
       </c>
       <c r="C5" s="30" t="n">
-        <v>93413752</v>
+        <v>98459888</v>
       </c>
       <c r="D5" s="31" t="n"/>
       <c r="E5" s="31" t="n">
@@ -1519,16 +1519,16 @@
         </is>
       </c>
       <c r="C6" s="32" t="n">
-        <v>7490560</v>
+        <v>7541601</v>
       </c>
       <c r="D6" s="33" t="n">
-        <v>0.008876669</v>
+        <v>0.008937156</v>
       </c>
       <c r="E6" s="33" t="n">
-        <v>-0.71</v>
+        <v>-0.717</v>
       </c>
       <c r="F6" s="33" t="n">
-        <v>1.121</v>
+        <v>1.132</v>
       </c>
     </row>
     <row r="7">
@@ -1543,16 +1543,16 @@
         </is>
       </c>
       <c r="C7" s="32" t="n">
-        <v>2241812</v>
+        <v>2297857</v>
       </c>
       <c r="D7" s="33" t="n">
-        <v>0.008784772999999999</v>
+        <v>0.009004392</v>
       </c>
       <c r="E7" s="33" t="n">
-        <v>6.134</v>
+        <v>6.209</v>
       </c>
       <c r="F7" s="33" t="n">
-        <v>-7.919</v>
+        <v>-8.015000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -1567,14 +1567,14 @@
         </is>
       </c>
       <c r="C8" s="32" t="n">
-        <v>7862805</v>
+        <v>7605610</v>
       </c>
       <c r="D8" s="33" t="n"/>
       <c r="E8" s="33" t="n">
-        <v>-2.938</v>
+        <v>-3.134</v>
       </c>
       <c r="F8" s="33" t="n">
-        <v>3797.173</v>
+        <v>4050.817</v>
       </c>
     </row>
     <row r="9">
@@ -1589,16 +1589,16 @@
         </is>
       </c>
       <c r="C9" s="32" t="n">
-        <v>3113569</v>
+        <v>2886093</v>
       </c>
       <c r="D9" s="33" t="n">
-        <v>0.005095986</v>
+        <v>0.0047236765</v>
       </c>
       <c r="E9" s="33" t="n">
-        <v>0.993</v>
+        <v>1.04</v>
       </c>
       <c r="F9" s="33" t="n">
-        <v>-1.313</v>
+        <v>-1.375</v>
       </c>
     </row>
     <row r="10">
@@ -1613,14 +1613,14 @@
         </is>
       </c>
       <c r="C10" s="32" t="n">
-        <v>1949429</v>
+        <v>1963401</v>
       </c>
       <c r="D10" s="33" t="n"/>
       <c r="E10" s="33" t="n">
-        <v>-0.484</v>
+        <v>-0.479</v>
       </c>
       <c r="F10" s="33" t="n">
-        <v>0.258</v>
+        <v>0.255</v>
       </c>
     </row>
     <row r="11">
@@ -1667,14 +1667,14 @@
         </is>
       </c>
       <c r="C13" s="32" t="n">
-        <v>1597930</v>
+        <v>1668405</v>
       </c>
       <c r="D13" s="33" t="n"/>
       <c r="E13" s="33" t="n">
-        <v>0.052</v>
+        <v>0.019</v>
       </c>
       <c r="F13" s="33" t="n">
-        <v>-1.059</v>
+        <v>-0.381</v>
       </c>
     </row>
     <row r="15">

--- a/app/reports/COE_research.xlsx
+++ b/app/reports/COE_research.xlsx
@@ -620,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-07-24 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-07-25 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>16.39</v>
+        <v>16.08</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.04672999858856201</v>
+        <v>0.04678999900817871</v>
       </c>
     </row>
     <row r="6">
@@ -1197,7 +1197,7 @@
         </is>
       </c>
       <c r="B35" s="20" t="n">
-        <v>6007314.704087858</v>
+        <v>6007314.925373135</v>
       </c>
     </row>
     <row r="36">
@@ -1218,7 +1218,7 @@
         </is>
       </c>
       <c r="B37" s="22" t="n">
-        <v>16.39</v>
+        <v>16.08</v>
       </c>
     </row>
     <row r="38">
@@ -1497,14 +1497,14 @@
         </is>
       </c>
       <c r="C5" s="30" t="n">
-        <v>98459888</v>
+        <v>96597624</v>
       </c>
       <c r="D5" s="31" t="n"/>
       <c r="E5" s="31" t="n">
-        <v>-4.41</v>
+        <v>-4.62</v>
       </c>
       <c r="F5" s="31" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="6">
@@ -1519,16 +1519,16 @@
         </is>
       </c>
       <c r="C6" s="32" t="n">
-        <v>7541601</v>
+        <v>7291695</v>
       </c>
       <c r="D6" s="33" t="n">
-        <v>0.008937156</v>
+        <v>0.0086410055</v>
       </c>
       <c r="E6" s="33" t="n">
-        <v>-0.717</v>
+        <v>-0.714</v>
       </c>
       <c r="F6" s="33" t="n">
-        <v>1.132</v>
+        <v>1.128</v>
       </c>
     </row>
     <row r="7">
@@ -1543,16 +1543,16 @@
         </is>
       </c>
       <c r="C7" s="32" t="n">
-        <v>2297857</v>
+        <v>2204448</v>
       </c>
       <c r="D7" s="33" t="n">
-        <v>0.009004392</v>
+        <v>0.008638359999999999</v>
       </c>
       <c r="E7" s="33" t="n">
-        <v>6.209</v>
+        <v>6.235</v>
       </c>
       <c r="F7" s="33" t="n">
-        <v>-8.015000000000001</v>
+        <v>-8.048999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -1567,14 +1567,14 @@
         </is>
       </c>
       <c r="C8" s="32" t="n">
-        <v>7605610</v>
+        <v>7421900</v>
       </c>
       <c r="D8" s="33" t="n"/>
       <c r="E8" s="33" t="n">
-        <v>-3.134</v>
+        <v>-2.896</v>
       </c>
       <c r="F8" s="33" t="n">
-        <v>4050.817</v>
+        <v>3742.821</v>
       </c>
     </row>
     <row r="9">
@@ -1589,16 +1589,16 @@
         </is>
       </c>
       <c r="C9" s="32" t="n">
-        <v>2886093</v>
+        <v>2900310</v>
       </c>
       <c r="D9" s="33" t="n">
-        <v>0.0047236765</v>
+        <v>0.004746946</v>
       </c>
       <c r="E9" s="33" t="n">
-        <v>1.04</v>
+        <v>1.049</v>
       </c>
       <c r="F9" s="33" t="n">
-        <v>-1.375</v>
+        <v>-1.386</v>
       </c>
     </row>
     <row r="10">
@@ -1613,14 +1613,14 @@
         </is>
       </c>
       <c r="C10" s="32" t="n">
-        <v>1963401</v>
+        <v>2023628</v>
       </c>
       <c r="D10" s="33" t="n"/>
       <c r="E10" s="33" t="n">
-        <v>-0.479</v>
+        <v>-0.484</v>
       </c>
       <c r="F10" s="33" t="n">
-        <v>0.255</v>
+        <v>0.258</v>
       </c>
     </row>
     <row r="11">
@@ -1667,14 +1667,14 @@
         </is>
       </c>
       <c r="C13" s="32" t="n">
-        <v>1668405</v>
+        <v>1712705</v>
       </c>
       <c r="D13" s="33" t="n"/>
       <c r="E13" s="33" t="n">
-        <v>0.019</v>
+        <v>0.047</v>
       </c>
       <c r="F13" s="33" t="n">
-        <v>-0.381</v>
+        <v>-0.9419999999999999</v>
       </c>
     </row>
     <row r="15">

--- a/app/reports/COE_research.xlsx
+++ b/app/reports/COE_research.xlsx
@@ -620,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-07-25 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-07-26 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
